--- a/research/traditional_assets/database/data/norway/norway_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ12"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04190000000000001</v>
+        <v>0.0581</v>
       </c>
       <c r="E2">
-        <v>0.0638</v>
+        <v>0.0665</v>
       </c>
       <c r="F2">
-        <v>0.105</v>
+        <v>0.1355</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3734.7</v>
+        <v>3335.3</v>
       </c>
       <c r="L2">
-        <v>0.461034231609614</v>
+        <v>0.4603398064952451</v>
       </c>
       <c r="M2">
-        <v>2149.85</v>
+        <v>3425.1776</v>
       </c>
       <c r="N2">
-        <v>0.05148934335729152</v>
+        <v>0.09871454674359757</v>
       </c>
       <c r="O2">
-        <v>0.5756419524995314</v>
+        <v>1.026947381045183</v>
       </c>
       <c r="P2">
-        <v>1932.15</v>
+        <v>3078.9776</v>
       </c>
       <c r="Q2">
-        <v>0.04627538422112743</v>
+        <v>0.08873696891445565</v>
       </c>
       <c r="R2">
-        <v>0.5173507912282111</v>
+        <v>0.9231486223128355</v>
       </c>
       <c r="S2">
-        <v>217.7</v>
+        <v>346.1999999999999</v>
       </c>
       <c r="T2">
-        <v>0.1012628788054981</v>
+        <v>0.1010750508236419</v>
       </c>
       <c r="U2">
-        <v>62649.13</v>
+        <v>42840.28</v>
       </c>
       <c r="V2">
-        <v>1.500459364888524</v>
+        <v>1.23466848042239</v>
       </c>
       <c r="W2">
-        <v>0.1149795929873181</v>
+        <v>0.07470078415187784</v>
       </c>
       <c r="X2">
-        <v>0.08946783870990986</v>
+        <v>0.1325305046456682</v>
       </c>
       <c r="Y2">
-        <v>0.02551175427740822</v>
+        <v>-0.05782972049379032</v>
       </c>
       <c r="Z2">
-        <v>0.04827067665588675</v>
+        <v>0.04859469557035939</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03736904023284179</v>
+        <v>0.06000009653068422</v>
       </c>
       <c r="AC2">
-        <v>-0.03736904023284179</v>
+        <v>-0.06000009653068422</v>
       </c>
       <c r="AD2">
-        <v>178139.05</v>
+        <v>153377.94</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>178139.05</v>
+        <v>153377.94</v>
       </c>
       <c r="AG2">
-        <v>115489.92</v>
+        <v>110537.66</v>
       </c>
       <c r="AH2">
-        <v>0.8101193606780773</v>
+        <v>0.8155115593324265</v>
       </c>
       <c r="AI2">
-        <v>0.8252876928675519</v>
+        <v>0.8376198258068137</v>
       </c>
       <c r="AJ2">
-        <v>0.7344667706499524</v>
+        <v>0.7610927799588336</v>
       </c>
       <c r="AK2">
-        <v>0.7538421892391287</v>
+        <v>0.788027292242693</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sparebanken Sør (OB:SOR)</t>
+          <t>Sparebanken Øst (OB:SPOG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0564</v>
+        <v>-0.011</v>
       </c>
       <c r="E3">
-        <v>0.0683</v>
+        <v>-0.0277</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,85 +731,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>141.4</v>
+        <v>27.5</v>
       </c>
       <c r="L3">
-        <v>0.4759340289464826</v>
+        <v>0.4407051282051282</v>
       </c>
       <c r="M3">
-        <v>80.7</v>
+        <v>10.7</v>
       </c>
       <c r="N3">
-        <v>0.3138856476079346</v>
+        <v>0.1081900910010111</v>
       </c>
       <c r="O3">
-        <v>0.5707213578500707</v>
+        <v>0.389090909090909</v>
       </c>
       <c r="P3">
-        <v>24.5</v>
+        <v>10.7</v>
       </c>
       <c r="Q3">
-        <v>0.09529366005445351</v>
+        <v>0.1081900910010111</v>
       </c>
       <c r="R3">
-        <v>0.1732673267326733</v>
+        <v>0.389090909090909</v>
       </c>
       <c r="S3">
-        <v>56.2</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.6964064436183396</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>91.59999999999999</v>
+        <v>48.6</v>
       </c>
       <c r="V3">
-        <v>0.3562816024893037</v>
+        <v>0.4914054600606673</v>
       </c>
       <c r="W3">
-        <v>0.09632808774439676</v>
+        <v>0.05180859080633007</v>
       </c>
       <c r="X3">
-        <v>0.5728529988458925</v>
+        <v>0.5067559871062027</v>
       </c>
       <c r="Y3">
-        <v>-0.4765249111014957</v>
+        <v>-0.4549473962998727</v>
       </c>
       <c r="Z3">
-        <v>0.03302689062552109</v>
+        <v>0.01814955934964079</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03671846595659062</v>
+        <v>0.05768286526408242</v>
       </c>
       <c r="AC3">
-        <v>-0.03671846595659062</v>
+        <v>-0.05768286526408242</v>
       </c>
       <c r="AD3">
-        <v>7447.4</v>
+        <v>2136.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7447.4</v>
+        <v>2136.4</v>
       </c>
       <c r="AG3">
-        <v>7355.799999999999</v>
+        <v>2087.8</v>
       </c>
       <c r="AH3">
-        <v>0.9666298916217795</v>
+        <v>0.9557553795911063</v>
       </c>
       <c r="AI3">
-        <v>0.8186474959328145</v>
+        <v>0.8308960796515246</v>
       </c>
       <c r="AJ3">
-        <v>0.966228375520498</v>
+        <v>0.9547720309141629</v>
       </c>
       <c r="AK3">
-        <v>0.8168028782091143</v>
+        <v>0.82763815111393</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sparebanken Øst (OB:SPOG)</t>
+          <t>Sparebanken Vest (OB:SVEG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0115</v>
+        <v>0.103</v>
       </c>
       <c r="E4">
-        <v>0.0165</v>
+        <v>0.167</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,28 +853,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>38.2</v>
+        <v>265.5</v>
       </c>
       <c r="L4">
-        <v>0.4510035419126329</v>
+        <v>0.555207026348808</v>
       </c>
       <c r="M4">
-        <v>18.5</v>
+        <v>113.2</v>
       </c>
       <c r="N4">
-        <v>0.137444279346211</v>
+        <v>0.1126592356687898</v>
       </c>
       <c r="O4">
-        <v>0.4842931937172775</v>
+        <v>0.4263653483992467</v>
       </c>
       <c r="P4">
-        <v>18.5</v>
+        <v>113.2</v>
       </c>
       <c r="Q4">
-        <v>0.137444279346211</v>
+        <v>0.1126592356687898</v>
       </c>
       <c r="R4">
-        <v>0.4842931937172775</v>
+        <v>0.4263653483992467</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -883,55 +883,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>40.8</v>
+        <v>128.6</v>
       </c>
       <c r="V4">
-        <v>0.3031203566121842</v>
+        <v>0.1279856687898089</v>
       </c>
       <c r="W4">
-        <v>0.07933541017653167</v>
+        <v>0.1185585424667322</v>
       </c>
       <c r="X4">
-        <v>0.4425969276941799</v>
+        <v>0.3050384144030213</v>
       </c>
       <c r="Y4">
-        <v>-0.3632615175176482</v>
+        <v>-0.1864798719362891</v>
       </c>
       <c r="Z4">
-        <v>0.02929174159634804</v>
+        <v>0.03080094038839329</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03673998535110967</v>
+        <v>0.05794580353886437</v>
       </c>
       <c r="AC4">
-        <v>-0.03673998535110967</v>
+        <v>-0.05794580353886437</v>
       </c>
       <c r="AD4">
-        <v>2948.1</v>
+        <v>11793.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2948.1</v>
+        <v>11793.7</v>
       </c>
       <c r="AG4">
-        <v>2907.3</v>
+        <v>11665.1</v>
       </c>
       <c r="AH4">
-        <v>0.9563369773250722</v>
+        <v>0.9214907997030902</v>
       </c>
       <c r="AI4">
-        <v>0.8474230360171319</v>
+        <v>0.8610551369662987</v>
       </c>
       <c r="AJ4">
-        <v>0.9557513396232618</v>
+        <v>0.9206939281288724</v>
       </c>
       <c r="AK4">
-        <v>0.845612402198889</v>
+        <v>0.8597382114060819</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sparebanken Vest (OB:SVEG)</t>
+          <t>Sparebanken Sør (OB:SOR)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,13 +957,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.07440000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="E5">
-        <v>0.112</v>
-      </c>
-      <c r="F5">
-        <v>0.112</v>
+        <v>0.039</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,85 +975,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>295.1</v>
+        <v>105.1</v>
       </c>
       <c r="L5">
-        <v>0.563598166539343</v>
+        <v>0.4428992836072482</v>
       </c>
       <c r="M5">
-        <v>71.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="N5">
-        <v>0.05871258712587125</v>
+        <v>0.1171303074670571</v>
       </c>
       <c r="O5">
-        <v>0.2426296170789563</v>
+        <v>0.6089438629876308</v>
       </c>
       <c r="P5">
-        <v>71.59999999999999</v>
+        <v>21.4</v>
       </c>
       <c r="Q5">
-        <v>0.05871258712587125</v>
+        <v>0.03916544655929722</v>
       </c>
       <c r="R5">
-        <v>0.2426296170789563</v>
+        <v>0.2036156041864891</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>42.6</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.665625</v>
       </c>
       <c r="U5">
-        <v>14.8</v>
+        <v>125.5</v>
       </c>
       <c r="V5">
-        <v>0.01213612136121361</v>
+        <v>0.2296852122986823</v>
       </c>
       <c r="W5">
-        <v>0.1562036840990896</v>
+        <v>0.06373173246012977</v>
       </c>
       <c r="X5">
-        <v>0.2398478199772738</v>
+        <v>0.3031112259446895</v>
       </c>
       <c r="Y5">
-        <v>-0.08364413587818426</v>
+        <v>-0.2393794934845598</v>
       </c>
       <c r="Z5">
-        <v>0.0353726422742258</v>
+        <v>0.02635231929282946</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03682428710920965</v>
+        <v>0.05795029429607979</v>
       </c>
       <c r="AC5">
-        <v>-0.03682428710920965</v>
+        <v>-0.05795029429607979</v>
       </c>
       <c r="AD5">
-        <v>13300.9</v>
+        <v>6361.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>13300.9</v>
+        <v>6361.8</v>
       </c>
       <c r="AG5">
-        <v>13286.1</v>
+        <v>6236.3</v>
       </c>
       <c r="AH5">
-        <v>0.9160147103385582</v>
+        <v>0.9209055904577169</v>
       </c>
       <c r="AI5">
-        <v>0.8558972478008791</v>
+        <v>0.8169245585874799</v>
       </c>
       <c r="AJ5">
-        <v>0.9159290205162144</v>
+        <v>0.9194421100741593</v>
       </c>
       <c r="AK5">
-        <v>0.8557598789088918</v>
+        <v>0.8139258679196033</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1070,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sbanken ASA (OB:SBANK)</t>
+          <t>SpareBank 1 Ostlandet (OB:SPOL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,13 +1079,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0323</v>
+        <v>0.0493</v>
       </c>
       <c r="E6">
-        <v>0.0059</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="F6">
-        <v>0.098</v>
+        <v>0.156</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1103,28 +1100,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>85.59999999999999</v>
+        <v>167.5</v>
       </c>
       <c r="L6">
-        <v>0.4273589615576635</v>
+        <v>0.4310344827586207</v>
       </c>
       <c r="M6">
-        <v>41.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="N6">
-        <v>0.03677311515791325</v>
+        <v>0.06975928135307741</v>
       </c>
       <c r="O6">
-        <v>0.4883177570093458</v>
+        <v>0.5934328358208956</v>
       </c>
       <c r="P6">
-        <v>41.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="Q6">
-        <v>0.03677311515791325</v>
+        <v>0.06975928135307741</v>
       </c>
       <c r="R6">
-        <v>0.4883177570093458</v>
+        <v>0.5934328358208956</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1133,55 +1130,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>191.9</v>
+        <v>189.7</v>
       </c>
       <c r="V6">
-        <v>0.1688220286795108</v>
+        <v>0.133132149624535</v>
       </c>
       <c r="W6">
-        <v>0.1081627495577458</v>
+        <v>0.07845065804880334</v>
       </c>
       <c r="X6">
-        <v>0.09294119038891377</v>
+        <v>0.1325305046456682</v>
       </c>
       <c r="Y6">
-        <v>0.015221559168832</v>
+        <v>-0.05407984659686481</v>
       </c>
       <c r="Z6">
-        <v>0.04921375921375921</v>
+        <v>0.05587347232207045</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.0371793925694997</v>
+        <v>0.0591273184542212</v>
       </c>
       <c r="AC6">
-        <v>-0.0371793925694997</v>
+        <v>-0.0591273184542212</v>
       </c>
       <c r="AD6">
-        <v>3341.4</v>
+        <v>4704.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>3341.4</v>
+        <v>4704.3</v>
       </c>
       <c r="AG6">
-        <v>3149.5</v>
+        <v>4514.6</v>
       </c>
       <c r="AH6">
-        <v>0.7461646680511824</v>
+        <v>0.7675226783266984</v>
       </c>
       <c r="AI6">
-        <v>0.788661253776435</v>
+        <v>0.724887128834923</v>
       </c>
       <c r="AJ6">
-        <v>0.7348000559936541</v>
+        <v>0.760097651317451</v>
       </c>
       <c r="AK6">
-        <v>0.7786348240994833</v>
+        <v>0.7166031746031747</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1198,7 +1195,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SpareBank 1 Østlandet (OB:SPOL)</t>
+          <t>Pareto Bank ASA (OB:PARB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1207,10 +1204,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.137</v>
+        <v>0.107</v>
       </c>
       <c r="E7">
-        <v>0.143</v>
+        <v>0.107</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1225,28 +1222,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>226.3</v>
+        <v>46.9</v>
       </c>
       <c r="L7">
-        <v>0.4445099194657238</v>
+        <v>0.5982142857142857</v>
       </c>
       <c r="M7">
-        <v>60.7</v>
+        <v>43</v>
       </c>
       <c r="N7">
-        <v>0.0317087185916523</v>
+        <v>0.1266195524146054</v>
       </c>
       <c r="O7">
-        <v>0.2682280159080866</v>
+        <v>0.9168443496801706</v>
       </c>
       <c r="P7">
-        <v>60.7</v>
+        <v>43</v>
       </c>
       <c r="Q7">
-        <v>0.0317087185916523</v>
+        <v>0.1266195524146054</v>
       </c>
       <c r="R7">
-        <v>0.2682280159080866</v>
+        <v>0.9168443496801706</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1255,55 +1252,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>86.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="V7">
-        <v>0.04497727628898292</v>
+        <v>0.2661955241460542</v>
       </c>
       <c r="W7">
-        <v>0.1281209307592142</v>
+        <v>0.1047108729627149</v>
       </c>
       <c r="X7">
-        <v>0.08599448703090595</v>
+        <v>0.1036336056741701</v>
       </c>
       <c r="Y7">
-        <v>0.04212644372830823</v>
+        <v>0.001077267288544834</v>
       </c>
       <c r="Z7">
-        <v>0.07802896773699135</v>
+        <v>0.08440090429540317</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.03723551002952572</v>
+        <v>0.06000009653068422</v>
       </c>
       <c r="AC7">
-        <v>-0.03723551002952572</v>
+        <v>-0.06000009653068422</v>
       </c>
       <c r="AD7">
-        <v>4906</v>
+        <v>641.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>4906</v>
+        <v>641.3</v>
       </c>
       <c r="AG7">
-        <v>4819.9</v>
+        <v>550.9</v>
       </c>
       <c r="AH7">
-        <v>0.7193231969268213</v>
+        <v>0.6537873381588337</v>
       </c>
       <c r="AI7">
-        <v>0.6954623421175736</v>
+        <v>0.6321963722397476</v>
       </c>
       <c r="AJ7">
-        <v>0.7157346084167384</v>
+        <v>0.6186412128017967</v>
       </c>
       <c r="AK7">
-        <v>0.6916994345742085</v>
+        <v>0.5962121212121212</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1320,7 +1317,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pareto Bank ASA (OB:PARB)</t>
+          <t>DNB Bank ASA (OB:DNB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1329,10 +1326,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.172</v>
+        <v>0.0581</v>
       </c>
       <c r="E8">
-        <v>0.195</v>
+        <v>0.0682</v>
+      </c>
+      <c r="F8">
+        <v>0.115</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1347,85 +1347,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>57.9</v>
+        <v>2664.6</v>
       </c>
       <c r="L8">
-        <v>0.6088328075709779</v>
+        <v>0.4599609880720167</v>
       </c>
       <c r="M8">
-        <v>17</v>
+        <v>3065.7</v>
       </c>
       <c r="N8">
-        <v>0.03603221704111912</v>
+        <v>0.1001872567378111</v>
       </c>
       <c r="O8">
-        <v>0.2936096718480138</v>
+        <v>1.150529160099077</v>
       </c>
       <c r="P8">
-        <v>17</v>
+        <v>2762.1</v>
       </c>
       <c r="Q8">
-        <v>0.03603221704111912</v>
+        <v>0.09026559083912587</v>
       </c>
       <c r="R8">
-        <v>0.2936096718480138</v>
+        <v>1.036590857914884</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>303.5999999999999</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.09903121636167921</v>
       </c>
       <c r="U8">
-        <v>202.4</v>
+        <v>42149.6</v>
       </c>
       <c r="V8">
-        <v>0.4289953370072064</v>
+        <v>1.377451412922349</v>
       </c>
       <c r="W8">
-        <v>0.1526898734177215</v>
+        <v>0.09221983802865646</v>
       </c>
       <c r="X8">
-        <v>0.06544781115531928</v>
+        <v>0.1500462387887835</v>
       </c>
       <c r="Y8">
-        <v>0.08724206226240225</v>
+        <v>-0.05782640076012707</v>
       </c>
       <c r="Z8">
-        <v>0.1281498450343619</v>
+        <v>0.05179356601442291</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.03750257043615786</v>
+        <v>0.06002575319616724</v>
       </c>
       <c r="AC8">
-        <v>-0.03750257043615786</v>
+        <v>-0.06002575319616724</v>
       </c>
       <c r="AD8">
-        <v>683.4</v>
+        <v>127234.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>683.4</v>
+        <v>127234.7</v>
       </c>
       <c r="AG8">
-        <v>481</v>
+        <v>85085.10000000001</v>
       </c>
       <c r="AH8">
-        <v>0.5915858725761772</v>
+        <v>0.8061278149756961</v>
       </c>
       <c r="AI8">
-        <v>0.6040837974012199</v>
+        <v>0.8462837523246501</v>
       </c>
       <c r="AJ8">
-        <v>0.5048278757346768</v>
+        <v>0.7354907472718974</v>
       </c>
       <c r="AK8">
-        <v>0.5178167725266444</v>
+        <v>0.7864007408804055</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.04190000000000001</v>
+        <v>0.0453</v>
       </c>
       <c r="E9">
-        <v>0.0593</v>
+        <v>0.06480000000000001</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1469,28 +1469,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>49.9</v>
+        <v>36.2</v>
       </c>
       <c r="L9">
-        <v>0.4821256038647343</v>
+        <v>0.4414634146341464</v>
       </c>
       <c r="M9">
-        <v>8.25</v>
+        <v>23.3</v>
       </c>
       <c r="N9">
-        <v>0.01407369498464688</v>
+        <v>0.04526908878958617</v>
       </c>
       <c r="O9">
-        <v>0.1653306613226453</v>
+        <v>0.643646408839779</v>
       </c>
       <c r="P9">
-        <v>8.25</v>
+        <v>23.3</v>
       </c>
       <c r="Q9">
-        <v>0.01407369498464688</v>
+        <v>0.04526908878958617</v>
       </c>
       <c r="R9">
-        <v>0.1653306613226453</v>
+        <v>0.643646408839779</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1499,55 +1499,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>10.1</v>
+        <v>8.56</v>
       </c>
       <c r="V9">
-        <v>0.01722961446605254</v>
+        <v>0.01663104721196814</v>
       </c>
       <c r="W9">
-        <v>0.1217964364168904</v>
+        <v>0.07470078415187784</v>
       </c>
       <c r="X9">
-        <v>0.05863448161899837</v>
+        <v>0.0845526443961592</v>
       </c>
       <c r="Y9">
-        <v>0.06316195479789204</v>
+        <v>-0.009851860244281363</v>
       </c>
       <c r="Z9">
-        <v>0.09828406468705785</v>
+        <v>0.07407407407407407</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.03765433480230944</v>
+        <v>0.06126791123877498</v>
       </c>
       <c r="AC9">
-        <v>-0.03765433480230944</v>
+        <v>-0.06126791123877498</v>
       </c>
       <c r="AD9">
-        <v>632.5</v>
+        <v>491.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>632.5</v>
+        <v>491.7</v>
       </c>
       <c r="AG9">
-        <v>622.4</v>
+        <v>483.14</v>
       </c>
       <c r="AH9">
-        <v>0.518995651103635</v>
+        <v>0.4885731319554849</v>
       </c>
       <c r="AI9">
-        <v>0.5661475116362334</v>
+        <v>0.5594493116395495</v>
       </c>
       <c r="AJ9">
-        <v>0.5149760052953831</v>
+        <v>0.4841858414174617</v>
       </c>
       <c r="AK9">
-        <v>0.5621895041098366</v>
+        <v>0.5551163912953558</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Komplett Bank ASA (OB:KOMP)</t>
+          <t>Lea Bank ASA (OB:LEA)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.0641</v>
+        <v>0.369</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1588,28 +1588,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>-20.2</v>
+        <v>10.6</v>
       </c>
       <c r="L10">
-        <v>-1.01</v>
+        <v>0.3642611683848797</v>
       </c>
       <c r="M10">
-        <v>16.3</v>
+        <v>5.8776</v>
       </c>
       <c r="N10">
-        <v>0.0992691839220463</v>
+        <v>0.07593798449612403</v>
       </c>
       <c r="O10">
-        <v>-0.806930693069307</v>
+        <v>0.5544905660377358</v>
       </c>
       <c r="P10">
-        <v>16.3</v>
+        <v>5.8776</v>
       </c>
       <c r="Q10">
-        <v>0.0992691839220463</v>
+        <v>0.07593798449612403</v>
       </c>
       <c r="R10">
-        <v>-0.806930693069307</v>
+        <v>0.5544905660377358</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1618,55 +1618,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>101.5</v>
+        <v>4.62</v>
       </c>
       <c r="V10">
-        <v>0.618148599269184</v>
+        <v>0.05968992248062015</v>
       </c>
       <c r="W10">
-        <v>-0.08451882845188284</v>
+        <v>0.06883116883116883</v>
       </c>
       <c r="X10">
-        <v>0.03957599179714175</v>
+        <v>0.06714658513342789</v>
       </c>
       <c r="Y10">
-        <v>-0.1240948202490246</v>
+        <v>0.001684583697740938</v>
       </c>
       <c r="Z10">
-        <v>0.2238638907544213</v>
+        <v>0.1816819629144034</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.03880498854679264</v>
+        <v>0.06429336917069177</v>
       </c>
       <c r="AC10">
-        <v>-0.03880498854679264</v>
+        <v>-0.06429336917069177</v>
       </c>
       <c r="AD10">
-        <v>7.45</v>
+        <v>8.06</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>7.45</v>
+        <v>8.06</v>
       </c>
       <c r="AG10">
-        <v>-94.05</v>
+        <v>3.44</v>
       </c>
       <c r="AH10">
-        <v>0.04340227206524906</v>
+        <v>0.09431312894921601</v>
       </c>
       <c r="AI10">
-        <v>0.03258254974852395</v>
+        <v>0.06034740940401318</v>
       </c>
       <c r="AJ10">
-        <v>-1.340698503207413</v>
+        <v>0.04255319148936171</v>
       </c>
       <c r="AK10">
-        <v>-0.7396775462052694</v>
+        <v>0.0266790755390104</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BRAbank ASA New (OB:BRA)</t>
+          <t>Komplett Bank ASA (OB:KOMP)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1691,6 +1691,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D11">
+        <v>0.143</v>
+      </c>
+      <c r="E11">
+        <v>-0.129</v>
+      </c>
       <c r="G11">
         <v>0</v>
       </c>
@@ -1704,10 +1710,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>50.9</v>
+        <v>11.4</v>
       </c>
       <c r="L11">
-        <v>1.471098265895954</v>
+        <v>0.1185031185031185</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1731,182 +1737,60 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>5.73</v>
+        <v>94.7</v>
       </c>
       <c r="V11">
-        <v>0.05325278810408923</v>
+        <v>1.036105032822757</v>
       </c>
       <c r="W11">
-        <v>0.9121863799283154</v>
+        <v>0.0515370705244123</v>
       </c>
       <c r="X11">
-        <v>0.04077862664347524</v>
+        <v>0.06635503870927445</v>
       </c>
       <c r="Y11">
-        <v>0.8714077532848402</v>
+        <v>-0.01481796818486215</v>
       </c>
       <c r="Z11">
-        <v>0.5005062924924056</v>
+        <v>0.7565867086118759</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.03888988685343446</v>
+        <v>0.06454586833053692</v>
       </c>
       <c r="AC11">
-        <v>-0.03888988685343446</v>
+        <v>-0.06454586833053692</v>
       </c>
       <c r="AD11">
-        <v>11.9</v>
+        <v>5.98</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>11.9</v>
+        <v>5.98</v>
       </c>
       <c r="AG11">
-        <v>6.17</v>
+        <v>-88.72</v>
       </c>
       <c r="AH11">
-        <v>0.09958158995815899</v>
+        <v>0.06140891353460669</v>
       </c>
       <c r="AI11">
-        <v>0.07172995780590717</v>
+        <v>0.03076448194258669</v>
       </c>
       <c r="AJ11">
-        <v>0.05423222290586271</v>
+        <v>-33.10447761194021</v>
       </c>
       <c r="AK11">
-        <v>0.03852157083099207</v>
+        <v>-0.8900481540930978</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>DNB Bank ASA (OB:DNB)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>0.03700000000000001</v>
-      </c>
-      <c r="E12">
-        <v>0.0349</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>2809.6</v>
-      </c>
-      <c r="L12">
-        <v>0.4507837694739038</v>
-      </c>
-      <c r="M12">
-        <v>1835</v>
-      </c>
-      <c r="N12">
-        <v>0.05131245228780833</v>
-      </c>
-      <c r="O12">
-        <v>0.653117881548975</v>
-      </c>
-      <c r="P12">
-        <v>1673.5</v>
-      </c>
-      <c r="Q12">
-        <v>0.04679639722269604</v>
-      </c>
-      <c r="R12">
-        <v>0.5956363895216401</v>
-      </c>
-      <c r="S12">
-        <v>161.5</v>
-      </c>
-      <c r="T12">
-        <v>0.0880108991825613</v>
-      </c>
-      <c r="U12">
-        <v>61904.2</v>
-      </c>
-      <c r="V12">
-        <v>1.731038860444111</v>
-      </c>
-      <c r="W12">
-        <v>0.1073706496275886</v>
-      </c>
-      <c r="X12">
-        <v>0.1134300449082478</v>
-      </c>
-      <c r="Y12">
-        <v>-0.006059395280659158</v>
-      </c>
-      <c r="Z12">
-        <v>0.04847317320524746</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0.04185732760076782</v>
-      </c>
-      <c r="AC12">
-        <v>-0.04185732760076782</v>
-      </c>
-      <c r="AD12">
-        <v>144860</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>144860</v>
-      </c>
-      <c r="AG12">
-        <v>82955.8</v>
-      </c>
-      <c r="AH12">
-        <v>0.8020095082916577</v>
-      </c>
-      <c r="AI12">
-        <v>0.8334853277008153</v>
-      </c>
-      <c r="AJ12">
-        <v>0.6987687536167915</v>
-      </c>
-      <c r="AK12">
-        <v>0.7413645337058218</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/norway/norway_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0581</v>
+        <v>0.0901</v>
       </c>
       <c r="E2">
-        <v>0.0665</v>
+        <v>0.107</v>
       </c>
       <c r="F2">
-        <v>0.1355</v>
+        <v>0.0641</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3335.3</v>
+        <v>4551.13</v>
       </c>
       <c r="L2">
-        <v>0.4603398064952451</v>
+        <v>0.5065704236325995</v>
       </c>
       <c r="M2">
-        <v>3425.1776</v>
+        <v>2270.7388</v>
       </c>
       <c r="N2">
-        <v>0.09871454674359757</v>
+        <v>0.06174210529177928</v>
       </c>
       <c r="O2">
-        <v>1.026947381045183</v>
+        <v>0.4989395600653025</v>
       </c>
       <c r="P2">
-        <v>3078.9776</v>
+        <v>2240.2388</v>
       </c>
       <c r="Q2">
-        <v>0.08873696891445565</v>
+        <v>0.06091280065691803</v>
       </c>
       <c r="R2">
-        <v>0.9231486223128355</v>
+        <v>0.4922379277234445</v>
       </c>
       <c r="S2">
-        <v>346.1999999999999</v>
+        <v>30.5</v>
       </c>
       <c r="T2">
-        <v>0.1010750508236419</v>
+        <v>0.01343175181575265</v>
       </c>
       <c r="U2">
-        <v>42840.28</v>
+        <v>63043.16</v>
       </c>
       <c r="V2">
-        <v>1.23466848042239</v>
+        <v>1.714163435550794</v>
       </c>
       <c r="W2">
-        <v>0.07470078415187784</v>
+        <v>0.1198531488280147</v>
       </c>
       <c r="X2">
-        <v>0.1325305046456682</v>
+        <v>0.09939146383283892</v>
       </c>
       <c r="Y2">
-        <v>-0.05782972049379032</v>
+        <v>0.02046168499517576</v>
       </c>
       <c r="Z2">
-        <v>0.04859469557035939</v>
+        <v>0.06407360712541986</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06000009653068422</v>
+        <v>0.05164192841419363</v>
       </c>
       <c r="AC2">
-        <v>-0.06000009653068422</v>
+        <v>-0.05164192841419363</v>
       </c>
       <c r="AD2">
-        <v>153377.94</v>
+        <v>168050.06</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>153377.94</v>
+        <v>168050.06</v>
       </c>
       <c r="AG2">
-        <v>110537.66</v>
+        <v>105006.9</v>
       </c>
       <c r="AH2">
-        <v>0.8155115593324265</v>
+        <v>0.8204453241858798</v>
       </c>
       <c r="AI2">
-        <v>0.8376198258068137</v>
+        <v>0.839955643560239</v>
       </c>
       <c r="AJ2">
-        <v>0.7610927799588336</v>
+        <v>0.7406081192117343</v>
       </c>
       <c r="AK2">
-        <v>0.788027292242693</v>
+        <v>0.7663226955271588</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.011</v>
+        <v>0.027</v>
       </c>
       <c r="E3">
-        <v>-0.0277</v>
+        <v>0.0142</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,85 +731,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>27.5</v>
+        <v>39.6</v>
       </c>
       <c r="L3">
-        <v>0.4407051282051282</v>
+        <v>0.4794188861985473</v>
       </c>
       <c r="M3">
-        <v>10.7</v>
+        <v>28.58</v>
       </c>
       <c r="N3">
-        <v>0.1081900910010111</v>
+        <v>0.2785575048732943</v>
       </c>
       <c r="O3">
-        <v>0.389090909090909</v>
+        <v>0.7217171717171716</v>
       </c>
       <c r="P3">
-        <v>10.7</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.1081900910010111</v>
+        <v>0.09532163742690059</v>
       </c>
       <c r="R3">
-        <v>0.389090909090909</v>
+        <v>0.246969696969697</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.6578026592022392</v>
       </c>
       <c r="U3">
-        <v>48.6</v>
+        <v>47.7</v>
       </c>
       <c r="V3">
-        <v>0.4914054600606673</v>
+        <v>0.4649122807017544</v>
       </c>
       <c r="W3">
-        <v>0.05180859080633007</v>
+        <v>0.09107635694572218</v>
       </c>
       <c r="X3">
-        <v>0.5067559871062027</v>
+        <v>0.374402712375099</v>
       </c>
       <c r="Y3">
-        <v>-0.4549473962998727</v>
+        <v>-0.2833263554293768</v>
       </c>
       <c r="Z3">
-        <v>0.01814955934964079</v>
+        <v>0.03274399429160389</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05768286526408242</v>
+        <v>0.04958311122693445</v>
       </c>
       <c r="AC3">
-        <v>-0.05768286526408242</v>
+        <v>-0.04958311122693445</v>
       </c>
       <c r="AD3">
-        <v>2136.4</v>
+        <v>2306.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2136.4</v>
+        <v>2306.4</v>
       </c>
       <c r="AG3">
-        <v>2087.8</v>
+        <v>2258.7</v>
       </c>
       <c r="AH3">
-        <v>0.9557553795911063</v>
+        <v>0.9574097135740972</v>
       </c>
       <c r="AI3">
-        <v>0.8308960796515246</v>
+        <v>0.8360459636785442</v>
       </c>
       <c r="AJ3">
-        <v>0.9547720309141629</v>
+        <v>0.9565493584042689</v>
       </c>
       <c r="AK3">
-        <v>0.82763815111393</v>
+        <v>0.833161195130948</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.103</v>
+        <v>0.1</v>
       </c>
       <c r="E4">
-        <v>0.167</v>
+        <v>0.146</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,28 +853,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>265.5</v>
+        <v>299.3</v>
       </c>
       <c r="L4">
-        <v>0.555207026348808</v>
+        <v>0.5542592592592592</v>
       </c>
       <c r="M4">
-        <v>113.2</v>
+        <v>145.2</v>
       </c>
       <c r="N4">
-        <v>0.1126592356687898</v>
+        <v>0.1227803145611365</v>
       </c>
       <c r="O4">
-        <v>0.4263653483992467</v>
+        <v>0.4851319746074172</v>
       </c>
       <c r="P4">
-        <v>113.2</v>
+        <v>145.2</v>
       </c>
       <c r="Q4">
-        <v>0.1126592356687898</v>
+        <v>0.1227803145611365</v>
       </c>
       <c r="R4">
-        <v>0.4263653483992467</v>
+        <v>0.4851319746074172</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -883,55 +883,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>128.6</v>
+        <v>20.4</v>
       </c>
       <c r="V4">
-        <v>0.1279856687898089</v>
+        <v>0.01725012683916793</v>
       </c>
       <c r="W4">
-        <v>0.1185585424667322</v>
+        <v>0.1572697178288056</v>
       </c>
       <c r="X4">
-        <v>0.3050384144030213</v>
+        <v>0.2191430181416944</v>
       </c>
       <c r="Y4">
-        <v>-0.1864798719362891</v>
+        <v>-0.06187330031288873</v>
       </c>
       <c r="Z4">
-        <v>0.03080094038839329</v>
+        <v>0.03979894164295927</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05794580353886437</v>
+        <v>0.04986994929994093</v>
       </c>
       <c r="AC4">
-        <v>-0.05794580353886437</v>
+        <v>-0.04986994929994093</v>
       </c>
       <c r="AD4">
-        <v>11793.7</v>
+        <v>13584.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>11793.7</v>
+        <v>13584.2</v>
       </c>
       <c r="AG4">
-        <v>11665.1</v>
+        <v>13563.8</v>
       </c>
       <c r="AH4">
-        <v>0.9214907997030902</v>
+        <v>0.9199149443345884</v>
       </c>
       <c r="AI4">
-        <v>0.8610551369662987</v>
+        <v>0.8635031624447764</v>
       </c>
       <c r="AJ4">
-        <v>0.9206939281288724</v>
+        <v>0.919804155590517</v>
       </c>
       <c r="AK4">
-        <v>0.8597382114060819</v>
+        <v>0.8633259288019298</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.052</v>
+        <v>0.0956</v>
       </c>
       <c r="E5">
-        <v>0.039</v>
+        <v>0.117</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,85 +975,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>105.1</v>
+        <v>170.1</v>
       </c>
       <c r="L5">
-        <v>0.4428992836072482</v>
+        <v>0.5197066911090742</v>
       </c>
       <c r="M5">
-        <v>64</v>
+        <v>63.2</v>
       </c>
       <c r="N5">
-        <v>0.1171303074670571</v>
+        <v>0.1070642046417076</v>
       </c>
       <c r="O5">
-        <v>0.6089438629876308</v>
+        <v>0.3715461493239272</v>
       </c>
       <c r="P5">
-        <v>21.4</v>
+        <v>51.5</v>
       </c>
       <c r="Q5">
-        <v>0.03916544655929722</v>
+        <v>0.08724377435202441</v>
       </c>
       <c r="R5">
-        <v>0.2036156041864891</v>
+        <v>0.3027630805408583</v>
       </c>
       <c r="S5">
-        <v>42.6</v>
+        <v>11.7</v>
       </c>
       <c r="T5">
-        <v>0.665625</v>
+        <v>0.1851265822784811</v>
       </c>
       <c r="U5">
-        <v>125.5</v>
+        <v>57.2</v>
       </c>
       <c r="V5">
-        <v>0.2296852122986823</v>
+        <v>0.09689988141622904</v>
       </c>
       <c r="W5">
-        <v>0.06373173246012977</v>
+        <v>0.1193684210526316</v>
       </c>
       <c r="X5">
-        <v>0.3031112259446895</v>
+        <v>0.2178578529909876</v>
       </c>
       <c r="Y5">
-        <v>-0.2393794934845598</v>
+        <v>-0.09848943193835605</v>
       </c>
       <c r="Z5">
-        <v>0.02635231929282946</v>
+        <v>0.04272120919426207</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05795029429607979</v>
+        <v>0.04987444662529109</v>
       </c>
       <c r="AC5">
-        <v>-0.05795029429607979</v>
+        <v>-0.04987444662529109</v>
       </c>
       <c r="AD5">
-        <v>6361.8</v>
+        <v>6726.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>6361.8</v>
+        <v>6726.9</v>
       </c>
       <c r="AG5">
-        <v>6236.3</v>
+        <v>6669.7</v>
       </c>
       <c r="AH5">
-        <v>0.9209055904577169</v>
+        <v>0.91932706499754</v>
       </c>
       <c r="AI5">
-        <v>0.8169245585874799</v>
+        <v>0.8133214039584568</v>
       </c>
       <c r="AJ5">
-        <v>0.9194421100741593</v>
+        <v>0.9186914600550964</v>
       </c>
       <c r="AK5">
-        <v>0.8139258679196033</v>
+        <v>0.8120213789157139</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SpareBank 1 Ostlandet (OB:SPOL)</t>
+          <t>SpareBank 1 Østlandet (OB:SPOL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1079,13 +1079,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0493</v>
+        <v>0.0578</v>
       </c>
       <c r="E6">
-        <v>0.08689999999999999</v>
-      </c>
-      <c r="F6">
-        <v>0.156</v>
+        <v>0.09720000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,28 +1097,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>167.5</v>
+        <v>212.2</v>
       </c>
       <c r="L6">
-        <v>0.4310344827586207</v>
+        <v>0.4576234634461936</v>
       </c>
       <c r="M6">
-        <v>99.40000000000001</v>
+        <v>101.8</v>
       </c>
       <c r="N6">
-        <v>0.06975928135307741</v>
+        <v>0.06721246533738282</v>
       </c>
       <c r="O6">
-        <v>0.5934328358208956</v>
+        <v>0.4797360980207352</v>
       </c>
       <c r="P6">
-        <v>99.40000000000001</v>
+        <v>101.8</v>
       </c>
       <c r="Q6">
-        <v>0.06975928135307741</v>
+        <v>0.06721246533738282</v>
       </c>
       <c r="R6">
-        <v>0.5934328358208956</v>
+        <v>0.4797360980207352</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1130,55 +1127,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>189.7</v>
+        <v>125.9</v>
       </c>
       <c r="V6">
-        <v>0.133132149624535</v>
+        <v>0.0831242572296316</v>
       </c>
       <c r="W6">
-        <v>0.07845065804880334</v>
+        <v>0.1198531488280147</v>
       </c>
       <c r="X6">
-        <v>0.1325305046456682</v>
+        <v>0.09939146383283892</v>
       </c>
       <c r="Y6">
-        <v>-0.05407984659686481</v>
+        <v>0.02046168499517576</v>
       </c>
       <c r="Z6">
-        <v>0.05587347232207045</v>
+        <v>0.07377766463540754</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.0591273184542212</v>
+        <v>0.05116600049538224</v>
       </c>
       <c r="AC6">
-        <v>-0.0591273184542212</v>
+        <v>-0.05116600049538224</v>
       </c>
       <c r="AD6">
-        <v>4704.3</v>
+        <v>4555.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>4704.3</v>
+        <v>4555.9</v>
       </c>
       <c r="AG6">
-        <v>4514.6</v>
+        <v>4430</v>
       </c>
       <c r="AH6">
-        <v>0.7675226783266984</v>
+        <v>0.7504983115064656</v>
       </c>
       <c r="AI6">
-        <v>0.724887128834923</v>
+        <v>0.7062534879394804</v>
       </c>
       <c r="AJ6">
-        <v>0.760097651317451</v>
+        <v>0.7452141439289439</v>
       </c>
       <c r="AK6">
-        <v>0.7166031746031747</v>
+        <v>0.7004063305348701</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1195,7 +1192,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pareto Bank ASA (OB:PARB)</t>
+          <t>DNB Bank ASA (OB:DNB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1204,11 +1201,14 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.107</v>
+        <v>0.0901</v>
       </c>
       <c r="E7">
         <v>0.107</v>
       </c>
+      <c r="F7">
+        <v>0.0641</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1222,28 +1222,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>46.9</v>
+        <v>3710.8</v>
       </c>
       <c r="L7">
-        <v>0.5982142857142857</v>
+        <v>0.5084750407651517</v>
       </c>
       <c r="M7">
-        <v>43</v>
+        <v>1904.6</v>
       </c>
       <c r="N7">
-        <v>0.1266195524146054</v>
+        <v>0.05887662678908158</v>
       </c>
       <c r="O7">
-        <v>0.9168443496801706</v>
+        <v>0.5132585965290503</v>
       </c>
       <c r="P7">
-        <v>43</v>
+        <v>1904.6</v>
       </c>
       <c r="Q7">
-        <v>0.1266195524146054</v>
+        <v>0.05887662678908158</v>
       </c>
       <c r="R7">
-        <v>0.9168443496801706</v>
+        <v>0.5132585965290503</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1252,55 +1252,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>90.40000000000001</v>
+        <v>62667</v>
       </c>
       <c r="V7">
-        <v>0.2661955241460542</v>
+        <v>1.937215988129463</v>
       </c>
       <c r="W7">
-        <v>0.1047108729627149</v>
+        <v>0.1608377362743101</v>
       </c>
       <c r="X7">
-        <v>0.1036336056741701</v>
+        <v>0.1178208740476747</v>
       </c>
       <c r="Y7">
-        <v>0.001077267288544834</v>
+        <v>0.04301686222663537</v>
       </c>
       <c r="Z7">
-        <v>0.08440090429540317</v>
+        <v>0.06747518417704666</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06000009653068422</v>
+        <v>0.05164192841419363</v>
       </c>
       <c r="AC7">
-        <v>-0.06000009653068422</v>
+        <v>-0.05164192841419363</v>
       </c>
       <c r="AD7">
-        <v>641.3</v>
+        <v>139516.1</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>641.3</v>
+        <v>139516.1</v>
       </c>
       <c r="AG7">
-        <v>550.9</v>
+        <v>76849.10000000001</v>
       </c>
       <c r="AH7">
-        <v>0.6537873381588337</v>
+        <v>0.8117767947070115</v>
       </c>
       <c r="AI7">
-        <v>0.6321963722397476</v>
+        <v>0.8492538385496052</v>
       </c>
       <c r="AJ7">
-        <v>0.6186412128017967</v>
+        <v>0.7037585818800877</v>
       </c>
       <c r="AK7">
-        <v>0.5962121212121212</v>
+        <v>0.7562860556341757</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DNB Bank ASA (OB:DNB)</t>
+          <t>Pareto Bank ASA (OB:PARB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1326,13 +1326,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0581</v>
+        <v>0.127</v>
       </c>
       <c r="E8">
-        <v>0.0682</v>
-      </c>
-      <c r="F8">
-        <v>0.115</v>
+        <v>0.137</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1347,85 +1344,82 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>2664.6</v>
+        <v>57.5</v>
       </c>
       <c r="L8">
-        <v>0.4599609880720167</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="M8">
-        <v>3065.7</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.1001872567378111</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>1.150529160099077</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>2762.1</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.09026559083912587</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>1.036590857914884</v>
+        <v>-0</v>
       </c>
       <c r="S8">
-        <v>303.5999999999999</v>
-      </c>
-      <c r="T8">
-        <v>0.09903121636167921</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>42149.6</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.377451412922349</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>0.09221983802865646</v>
+        <v>0.1541141785044224</v>
       </c>
       <c r="X8">
-        <v>0.1500462387887835</v>
+        <v>0.08422390827228696</v>
       </c>
       <c r="Y8">
-        <v>-0.05782640076012707</v>
+        <v>0.06989027023213545</v>
       </c>
       <c r="Z8">
-        <v>0.05179356601442291</v>
+        <v>0.1020562770562771</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06002575319616724</v>
+        <v>0.05186460672116278</v>
       </c>
       <c r="AC8">
-        <v>-0.06002575319616724</v>
+        <v>-0.05186460672116278</v>
       </c>
       <c r="AD8">
-        <v>127234.7</v>
+        <v>789.3</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>127234.7</v>
+        <v>789.3</v>
       </c>
       <c r="AG8">
-        <v>85085.10000000001</v>
+        <v>789.3</v>
       </c>
       <c r="AH8">
-        <v>0.8061278149756961</v>
+        <v>0.6591782194755302</v>
       </c>
       <c r="AI8">
-        <v>0.8462837523246501</v>
+        <v>0.6342306147047007</v>
       </c>
       <c r="AJ8">
-        <v>0.7354907472718974</v>
+        <v>0.6591782194755302</v>
       </c>
       <c r="AK8">
-        <v>0.7864007408804055</v>
+        <v>0.6342306147047007</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1451,10 +1445,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0453</v>
+        <v>0.06509999999999999</v>
       </c>
       <c r="E9">
-        <v>0.06480000000000001</v>
+        <v>0.0733</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1469,28 +1463,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>36.2</v>
+        <v>46.9</v>
       </c>
       <c r="L9">
-        <v>0.4414634146341464</v>
+        <v>0.4625246548323471</v>
       </c>
       <c r="M9">
-        <v>23.3</v>
+        <v>18.6</v>
       </c>
       <c r="N9">
-        <v>0.04526908878958617</v>
+        <v>0.03964194373401535</v>
       </c>
       <c r="O9">
-        <v>0.643646408839779</v>
+        <v>0.396588486140725</v>
       </c>
       <c r="P9">
-        <v>23.3</v>
+        <v>18.6</v>
       </c>
       <c r="Q9">
-        <v>0.04526908878958617</v>
+        <v>0.03964194373401535</v>
       </c>
       <c r="R9">
-        <v>0.643646408839779</v>
+        <v>0.396588486140725</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1499,55 +1493,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>8.56</v>
+        <v>8.44</v>
       </c>
       <c r="V9">
-        <v>0.01663104721196814</v>
+        <v>0.01798806479113384</v>
       </c>
       <c r="W9">
-        <v>0.07470078415187784</v>
+        <v>0.1211573236889693</v>
       </c>
       <c r="X9">
-        <v>0.0845526443961592</v>
+        <v>0.07339110544825259</v>
       </c>
       <c r="Y9">
-        <v>-0.009851860244281363</v>
+        <v>0.04776621824071667</v>
       </c>
       <c r="Z9">
-        <v>0.07407407407407407</v>
+        <v>0.1165195808052951</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06126791123877498</v>
+        <v>0.05278740478001585</v>
       </c>
       <c r="AC9">
-        <v>-0.06126791123877498</v>
+        <v>-0.05278740478001585</v>
       </c>
       <c r="AD9">
-        <v>491.7</v>
+        <v>547.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>491.7</v>
+        <v>547.6</v>
       </c>
       <c r="AG9">
-        <v>483.14</v>
+        <v>539.16</v>
       </c>
       <c r="AH9">
-        <v>0.4885731319554849</v>
+        <v>0.5385523210070811</v>
       </c>
       <c r="AI9">
-        <v>0.5594493116395495</v>
+        <v>0.5676376075463875</v>
       </c>
       <c r="AJ9">
-        <v>0.4841858414174617</v>
+        <v>0.5346899916696418</v>
       </c>
       <c r="AK9">
-        <v>0.5551163912953558</v>
+        <v>0.5638215548072699</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1564,7 +1558,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lea Bank ASA (OB:LEA)</t>
+          <t>Morrow Bank ASA (OB:MOBA)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1573,7 +1567,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.369</v>
+        <v>-0.0765</v>
+      </c>
+      <c r="E10">
+        <v>-0.381</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1588,28 +1585,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>10.6</v>
+        <v>2.63</v>
       </c>
       <c r="L10">
-        <v>0.3642611683848797</v>
+        <v>0.05831485587583148</v>
       </c>
       <c r="M10">
-        <v>5.8776</v>
+        <v>2.19</v>
       </c>
       <c r="N10">
-        <v>0.07593798449612403</v>
+        <v>0.02482993197278911</v>
       </c>
       <c r="O10">
-        <v>0.5544905660377358</v>
+        <v>0.8326996197718631</v>
       </c>
       <c r="P10">
-        <v>5.8776</v>
+        <v>2.19</v>
       </c>
       <c r="Q10">
-        <v>0.07593798449612403</v>
+        <v>0.02482993197278911</v>
       </c>
       <c r="R10">
-        <v>0.5544905660377358</v>
+        <v>0.8326996197718631</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1618,55 +1615,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>4.62</v>
+        <v>111.7</v>
       </c>
       <c r="V10">
-        <v>0.05968992248062015</v>
+        <v>1.266439909297052</v>
       </c>
       <c r="W10">
-        <v>0.06883116883116883</v>
+        <v>0.01395966029723991</v>
       </c>
       <c r="X10">
-        <v>0.06714658513342789</v>
+        <v>0.05938943966019991</v>
       </c>
       <c r="Y10">
-        <v>0.001684583697740938</v>
+        <v>-0.04542977936296</v>
       </c>
       <c r="Z10">
-        <v>0.1816819629144034</v>
+        <v>0.4524478330658107</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.06429336917069177</v>
+        <v>0.05576391946026646</v>
       </c>
       <c r="AC10">
-        <v>-0.06429336917069177</v>
+        <v>-0.05576391946026646</v>
       </c>
       <c r="AD10">
-        <v>8.06</v>
+        <v>15.5</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>8.06</v>
+        <v>15.5</v>
       </c>
       <c r="AG10">
-        <v>3.44</v>
+        <v>-96.2</v>
       </c>
       <c r="AH10">
-        <v>0.09431312894921601</v>
+        <v>0.1494696239151398</v>
       </c>
       <c r="AI10">
-        <v>0.06034740940401318</v>
+        <v>0.0684931506849315</v>
       </c>
       <c r="AJ10">
-        <v>0.04255319148936171</v>
+        <v>12.025</v>
       </c>
       <c r="AK10">
-        <v>0.0266790755390104</v>
+        <v>-0.8394415357766143</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1683,7 +1680,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Komplett Bank ASA (OB:KOMP)</t>
+          <t>Lea Bank ASA (OB:LEA)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1692,10 +1689,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.143</v>
+        <v>0.198</v>
       </c>
       <c r="E11">
-        <v>-0.129</v>
+        <v>0.234</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1710,82 +1707,85 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="L11">
-        <v>0.1185031185031185</v>
+        <v>0.3793103448275862</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>6.5688</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.08973770491803279</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>0.5428760330578513</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>6.5688</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.08973770491803279</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0.5428760330578513</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
       <c r="U11">
-        <v>94.7</v>
+        <v>4.82</v>
       </c>
       <c r="V11">
-        <v>1.036105032822757</v>
+        <v>0.06584699453551912</v>
       </c>
       <c r="W11">
-        <v>0.0515370705244123</v>
+        <v>0.09641434262948206</v>
       </c>
       <c r="X11">
-        <v>0.06635503870927445</v>
+        <v>0.05848182544026859</v>
       </c>
       <c r="Y11">
-        <v>-0.01481796818486215</v>
+        <v>0.03793251718921348</v>
       </c>
       <c r="Z11">
-        <v>0.7565867086118759</v>
+        <v>0.2474018923530324</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.06454586833053692</v>
+        <v>0.05614010949640685</v>
       </c>
       <c r="AC11">
-        <v>-0.06454586833053692</v>
+        <v>-0.05614010949640685</v>
       </c>
       <c r="AD11">
-        <v>5.98</v>
+        <v>8.16</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>5.98</v>
+        <v>8.16</v>
       </c>
       <c r="AG11">
-        <v>-88.72</v>
+        <v>3.34</v>
       </c>
       <c r="AH11">
-        <v>0.06140891353460669</v>
+        <v>0.1002949852507375</v>
       </c>
       <c r="AI11">
-        <v>0.03076448194258669</v>
+        <v>0.05748098055790363</v>
       </c>
       <c r="AJ11">
-        <v>-33.10447761194021</v>
+        <v>0.04363731382283773</v>
       </c>
       <c r="AK11">
-        <v>-0.8900481540930978</v>
+        <v>0.02435467405570949</v>
       </c>
       <c r="AL11">
         <v>0</v>

--- a/research/traditional_assets/database/data/norway/norway_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0867</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="E2">
-        <v>0.09810000000000001</v>
+        <v>0.105</v>
       </c>
       <c r="F2">
         <v>-0.0175</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>4040</v>
+        <v>5171.14</v>
       </c>
       <c r="L2">
-        <v>0.5135963183788662</v>
+        <v>0.5200366057241698</v>
       </c>
       <c r="M2">
-        <v>3658.5</v>
+        <v>4145.24</v>
       </c>
       <c r="N2">
-        <v>0.1235462171252583</v>
+        <v>0.1196959984291712</v>
       </c>
       <c r="O2">
-        <v>0.905569306930693</v>
+        <v>0.8016104766067056</v>
       </c>
       <c r="P2">
-        <v>2448.3</v>
+        <v>2911.43</v>
       </c>
       <c r="Q2">
-        <v>0.08267820237468088</v>
+        <v>0.08406908181592428</v>
       </c>
       <c r="R2">
-        <v>0.6060148514851486</v>
+        <v>0.5630151185231883</v>
       </c>
       <c r="S2">
-        <v>1210.2</v>
+        <v>1233.81</v>
       </c>
       <c r="T2">
-        <v>0.3307913079130791</v>
+        <v>0.2976450096978703</v>
       </c>
       <c r="U2">
-        <v>57083.9</v>
+        <v>57556.58</v>
       </c>
       <c r="V2">
-        <v>1.927702584052627</v>
+        <v>1.661976703223087</v>
       </c>
       <c r="W2">
-        <v>0.1632481533562851</v>
+        <v>0.1445518453427065</v>
       </c>
       <c r="X2">
-        <v>0.1292248969684605</v>
+        <v>0.09979012394369728</v>
       </c>
       <c r="Y2">
-        <v>0.03402325638782461</v>
+        <v>0.0447617213990092</v>
       </c>
       <c r="Z2">
-        <v>0.0774247588750422</v>
+        <v>0.07271065418237259</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05588457980933885</v>
+        <v>0.05611893927318358</v>
       </c>
       <c r="AC2">
-        <v>-0.05588457980933885</v>
+        <v>-0.05611893927318358</v>
       </c>
       <c r="AD2">
-        <v>147734.5</v>
+        <v>178917.05</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>147734.5</v>
+        <v>178917.05</v>
       </c>
       <c r="AG2">
-        <v>90650.60000000001</v>
+        <v>121360.47</v>
       </c>
       <c r="AH2">
-        <v>0.833025556127567</v>
+        <v>0.8378288393102362</v>
       </c>
       <c r="AI2">
-        <v>0.847414898285203</v>
+        <v>0.8379053519440807</v>
       </c>
       <c r="AJ2">
-        <v>0.7537696548398095</v>
+        <v>0.7779922761359294</v>
       </c>
       <c r="AK2">
-        <v>0.7731288954692302</v>
+        <v>0.7780895423977977</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,120 +704,1093 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Sparebanken Øst (OB:SPOG)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.131</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>49.7</v>
+      </c>
+      <c r="L3">
+        <v>0.5107913669064749</v>
+      </c>
+      <c r="M3">
+        <v>28</v>
+      </c>
+      <c r="N3">
+        <v>0.2132520944402132</v>
+      </c>
+      <c r="O3">
+        <v>0.5633802816901408</v>
+      </c>
+      <c r="P3">
+        <v>13.7</v>
+      </c>
+      <c r="Q3">
+        <v>0.1043412033511043</v>
+      </c>
+      <c r="R3">
+        <v>0.2756539235412475</v>
+      </c>
+      <c r="S3">
+        <v>14.3</v>
+      </c>
+      <c r="T3">
+        <v>0.5107142857142858</v>
+      </c>
+      <c r="U3">
+        <v>24.4</v>
+      </c>
+      <c r="V3">
+        <v>0.1858339680121858</v>
+      </c>
+      <c r="W3">
+        <v>0.1098828211364139</v>
+      </c>
+      <c r="X3">
+        <v>0.2943939215381816</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1845111004017677</v>
+      </c>
+      <c r="Z3">
+        <v>0.03589081519734415</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0.05419535548486964</v>
+      </c>
+      <c r="AC3">
+        <v>-0.05419535548486964</v>
+      </c>
+      <c r="AD3">
+        <v>2286.8</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>2286.8</v>
+      </c>
+      <c r="AG3">
+        <v>2262.4</v>
+      </c>
+      <c r="AH3">
+        <v>0.9457011703403498</v>
+      </c>
+      <c r="AI3">
+        <v>0.8306876384903193</v>
+      </c>
+      <c r="AJ3">
+        <v>0.9451476793248944</v>
+      </c>
+      <c r="AK3">
+        <v>0.8291735385743083</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sparebanken Vest (OB:SVEG)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.128</v>
+      </c>
+      <c r="E4">
+        <v>0.182</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>434</v>
+      </c>
+      <c r="L4">
+        <v>0.6243705941591138</v>
+      </c>
+      <c r="M4">
+        <v>290.2</v>
+      </c>
+      <c r="N4">
+        <v>0.2121189971493312</v>
+      </c>
+      <c r="O4">
+        <v>0.6686635944700461</v>
+      </c>
+      <c r="P4">
+        <v>290.2</v>
+      </c>
+      <c r="Q4">
+        <v>0.2121189971493312</v>
+      </c>
+      <c r="R4">
+        <v>0.6686635944700461</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>34.6</v>
+      </c>
+      <c r="V4">
+        <v>0.02529054893648125</v>
+      </c>
+      <c r="W4">
+        <v>0.2021142830531365</v>
+      </c>
+      <c r="X4">
+        <v>0.2151758855999415</v>
+      </c>
+      <c r="Y4">
+        <v>-0.01306160254680502</v>
+      </c>
+      <c r="Z4">
+        <v>0.04424260554639713</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.05443287951567607</v>
+      </c>
+      <c r="AC4">
+        <v>-0.05443287951567607</v>
+      </c>
+      <c r="AD4">
+        <v>15675.7</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>15675.7</v>
+      </c>
+      <c r="AG4">
+        <v>15641.1</v>
+      </c>
+      <c r="AH4">
+        <v>0.9197303418251799</v>
+      </c>
+      <c r="AI4">
+        <v>0.8685127625506264</v>
+      </c>
+      <c r="AJ4">
+        <v>0.9195670578275286</v>
+      </c>
+      <c r="AK4">
+        <v>0.8682602154954675</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sparebanken Sør (OB:SOR)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.106</v>
+      </c>
+      <c r="E5">
+        <v>0.139</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>189</v>
+      </c>
+      <c r="L5">
+        <v>0.5193734542456719</v>
+      </c>
+      <c r="M5">
+        <v>98.51000000000001</v>
+      </c>
+      <c r="N5">
+        <v>0.13567001790387</v>
+      </c>
+      <c r="O5">
+        <v>0.5212169312169312</v>
+      </c>
+      <c r="P5">
+        <v>89.2</v>
+      </c>
+      <c r="Q5">
+        <v>0.1228480925492356</v>
+      </c>
+      <c r="R5">
+        <v>0.471957671957672</v>
+      </c>
+      <c r="S5">
+        <v>9.310000000000002</v>
+      </c>
+      <c r="T5">
+        <v>0.09450817175921228</v>
+      </c>
+      <c r="U5">
+        <v>32.3</v>
+      </c>
+      <c r="V5">
+        <v>0.04448423082220079</v>
+      </c>
+      <c r="W5">
+        <v>0.1224331152425989</v>
+      </c>
+      <c r="X5">
+        <v>0.1996920305594083</v>
+      </c>
+      <c r="Y5">
+        <v>-0.07725891531680934</v>
+      </c>
+      <c r="Z5">
+        <v>0.04430564686974944</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.05450858884515877</v>
+      </c>
+      <c r="AC5">
+        <v>-0.05450858884515877</v>
+      </c>
+      <c r="AD5">
+        <v>7474</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>7474</v>
+      </c>
+      <c r="AG5">
+        <v>7441.7</v>
+      </c>
+      <c r="AH5">
+        <v>0.9114522993622028</v>
+      </c>
+      <c r="AI5">
+        <v>0.8154759306943655</v>
+      </c>
+      <c r="AJ5">
+        <v>0.9111021327652489</v>
+      </c>
+      <c r="AK5">
+        <v>0.8148233310339542</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>DNB Bank ASA (OB:DNB)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D6">
         <v>0.0867</v>
       </c>
-      <c r="E3">
+      <c r="E6">
         <v>0.09810000000000001</v>
       </c>
-      <c r="F3">
+      <c r="F6">
         <v>-0.0175</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>4040</v>
       </c>
-      <c r="L3">
+      <c r="L6">
         <v>0.5135963183788662</v>
       </c>
-      <c r="M3">
+      <c r="M6">
         <v>3658.5</v>
       </c>
-      <c r="N3">
+      <c r="N6">
         <v>0.1235462171252583</v>
       </c>
-      <c r="O3">
+      <c r="O6">
         <v>0.905569306930693</v>
       </c>
-      <c r="P3">
+      <c r="P6">
         <v>2448.3</v>
       </c>
-      <c r="Q3">
+      <c r="Q6">
         <v>0.08267820237468088</v>
       </c>
-      <c r="R3">
+      <c r="R6">
         <v>0.6060148514851486</v>
       </c>
-      <c r="S3">
+      <c r="S6">
         <v>1210.2</v>
       </c>
-      <c r="T3">
+      <c r="T6">
         <v>0.3307913079130791</v>
       </c>
-      <c r="U3">
+      <c r="U6">
         <v>57083.9</v>
       </c>
-      <c r="V3">
+      <c r="V6">
         <v>1.927702584052627</v>
       </c>
-      <c r="W3">
+      <c r="W6">
         <v>0.1632481533562851</v>
       </c>
-      <c r="X3">
-        <v>0.1292248969684605</v>
-      </c>
-      <c r="Y3">
-        <v>0.03402325638782461</v>
-      </c>
-      <c r="Z3">
+      <c r="X6">
+        <v>0.1291712621770616</v>
+      </c>
+      <c r="Y6">
+        <v>0.03407689117922344</v>
+      </c>
+      <c r="Z6">
         <v>0.0774247588750422</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.05588457980933885</v>
-      </c>
-      <c r="AC3">
-        <v>-0.05588457980933885</v>
-      </c>
-      <c r="AD3">
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.05587562416987282</v>
+      </c>
+      <c r="AC6">
+        <v>-0.05587562416987282</v>
+      </c>
+      <c r="AD6">
         <v>147734.5</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
         <v>147734.5</v>
       </c>
-      <c r="AG3">
+      <c r="AG6">
         <v>90650.60000000001</v>
       </c>
-      <c r="AH3">
+      <c r="AH6">
         <v>0.833025556127567</v>
       </c>
-      <c r="AI3">
+      <c r="AI6">
         <v>0.847414898285203</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ6">
         <v>0.7537696548398095</v>
       </c>
-      <c r="AK3">
+      <c r="AK6">
         <v>0.7731288954692302</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SpareBank 1 Østlandet (OB:SPOL)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0859</v>
+      </c>
+      <c r="E7">
+        <v>0.105</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>306.2</v>
+      </c>
+      <c r="L7">
+        <v>0.5064505458154152</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>-0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>63.7</v>
+      </c>
+      <c r="V7">
+        <v>0.03962921488117457</v>
+      </c>
+      <c r="W7">
+        <v>0.1637170507405229</v>
+      </c>
+      <c r="X7">
+        <v>0.09979012394369728</v>
+      </c>
+      <c r="Y7">
+        <v>0.06392692679682561</v>
+      </c>
+      <c r="Z7">
+        <v>0.09596368426900306</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.05611893927318358</v>
+      </c>
+      <c r="AC7">
+        <v>-0.05611893927318358</v>
+      </c>
+      <c r="AD7">
+        <v>4466.9</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>4466.9</v>
+      </c>
+      <c r="AG7">
+        <v>4403.2</v>
+      </c>
+      <c r="AH7">
+        <v>0.7353769158586175</v>
+      </c>
+      <c r="AI7">
+        <v>0.6763111676356589</v>
+      </c>
+      <c r="AJ7">
+        <v>0.7325724553289188</v>
+      </c>
+      <c r="AK7">
+        <v>0.6731589488006604</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pareto Bank ASA (OB:PARB)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.129</v>
+      </c>
+      <c r="E8">
+        <v>0.137</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>65.8</v>
+      </c>
+      <c r="L8">
+        <v>0.6143790849673203</v>
+      </c>
+      <c r="M8">
+        <v>32.9</v>
+      </c>
+      <c r="N8">
+        <v>0.07200700372072663</v>
+      </c>
+      <c r="O8">
+        <v>0.5</v>
+      </c>
+      <c r="P8">
+        <v>32.9</v>
+      </c>
+      <c r="Q8">
+        <v>0.07200700372072663</v>
+      </c>
+      <c r="R8">
+        <v>0.5</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>183.3</v>
+      </c>
+      <c r="V8">
+        <v>0.4011818778726199</v>
+      </c>
+      <c r="W8">
+        <v>0.1445518453427065</v>
+      </c>
+      <c r="X8">
+        <v>0.08500246556420532</v>
+      </c>
+      <c r="Y8">
+        <v>0.05954937977850117</v>
+      </c>
+      <c r="Z8">
+        <v>0.105195953246243</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.05712842458657699</v>
+      </c>
+      <c r="AC8">
+        <v>-0.05712842458657699</v>
+      </c>
+      <c r="AD8">
+        <v>761.5</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>761.5</v>
+      </c>
+      <c r="AG8">
+        <v>578.2</v>
+      </c>
+      <c r="AH8">
+        <v>0.625</v>
+      </c>
+      <c r="AI8">
+        <v>0.6025001978004588</v>
+      </c>
+      <c r="AJ8">
+        <v>0.5585933726210029</v>
+      </c>
+      <c r="AK8">
+        <v>0.5350731075328522</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SpareBank 1 Ringerike Hadeland (OB:RING)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0824</v>
+      </c>
+      <c r="E9">
+        <v>0.0793</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>60.3</v>
+      </c>
+      <c r="L9">
+        <v>0.481245011971269</v>
+      </c>
+      <c r="M9">
+        <v>29.7</v>
+      </c>
+      <c r="N9">
+        <v>0.06553398058252427</v>
+      </c>
+      <c r="O9">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="P9">
+        <v>29.7</v>
+      </c>
+      <c r="Q9">
+        <v>0.06553398058252427</v>
+      </c>
+      <c r="R9">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="V9">
+        <v>0.02157987643424537</v>
+      </c>
+      <c r="W9">
+        <v>0.1446043165467626</v>
+      </c>
+      <c r="X9">
+        <v>0.0770310919684568</v>
+      </c>
+      <c r="Y9">
+        <v>0.06757322457830579</v>
+      </c>
+      <c r="Z9">
+        <v>0.1310450133868808</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.06053919009404848</v>
+      </c>
+      <c r="AC9">
+        <v>-0.06053919009404848</v>
+      </c>
+      <c r="AD9">
+        <v>483.6</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>483.6</v>
+      </c>
+      <c r="AG9">
+        <v>473.8200000000001</v>
+      </c>
+      <c r="AH9">
+        <v>0.5162254483347567</v>
+      </c>
+      <c r="AI9">
+        <v>0.506334415244477</v>
+      </c>
+      <c r="AJ9">
+        <v>0.5111216586481414</v>
+      </c>
+      <c r="AK9">
+        <v>0.5012270977023654</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Morrow Bank ASA (OB:MOBA)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>-0.0793</v>
+      </c>
+      <c r="E10">
+        <v>-0.103</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>17.4</v>
+      </c>
+      <c r="L10">
+        <v>0.3210332103321033</v>
+      </c>
+      <c r="M10">
+        <v>2.46</v>
+      </c>
+      <c r="N10">
+        <v>0.01304347826086957</v>
+      </c>
+      <c r="O10">
+        <v>0.1413793103448276</v>
+      </c>
+      <c r="P10">
+        <v>2.46</v>
+      </c>
+      <c r="Q10">
+        <v>0.01304347826086957</v>
+      </c>
+      <c r="R10">
+        <v>0.1413793103448276</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>63.7</v>
+      </c>
+      <c r="V10">
+        <v>0.3377518557794274</v>
+      </c>
+      <c r="W10">
+        <v>0.08254269449715369</v>
+      </c>
+      <c r="X10">
+        <v>0.06462094303227245</v>
+      </c>
+      <c r="Y10">
+        <v>0.01792175146488124</v>
+      </c>
+      <c r="Z10">
+        <v>0.4729493891797557</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.06208833796018046</v>
+      </c>
+      <c r="AC10">
+        <v>-0.06208833796018046</v>
+      </c>
+      <c r="AD10">
+        <v>25.2</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>25.2</v>
+      </c>
+      <c r="AG10">
+        <v>-38.5</v>
+      </c>
+      <c r="AH10">
+        <v>0.117867165575304</v>
+      </c>
+      <c r="AI10">
+        <v>0.09905660377358491</v>
+      </c>
+      <c r="AJ10">
+        <v>-0.2564956695536309</v>
+      </c>
+      <c r="AK10">
+        <v>-0.2018877818563188</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Lea Bank ASA (OB:LEA)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.143</v>
+      </c>
+      <c r="E11">
+        <v>0.067</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>8.74</v>
+      </c>
+      <c r="L11">
+        <v>0.2894039735099338</v>
+      </c>
+      <c r="M11">
+        <v>4.97</v>
+      </c>
+      <c r="N11">
+        <v>0.0568649885583524</v>
+      </c>
+      <c r="O11">
+        <v>0.568649885583524</v>
+      </c>
+      <c r="P11">
+        <v>4.97</v>
+      </c>
+      <c r="Q11">
+        <v>0.0568649885583524</v>
+      </c>
+      <c r="R11">
+        <v>0.568649885583524</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>60.9</v>
+      </c>
+      <c r="V11">
+        <v>0.6967963386727688</v>
+      </c>
+      <c r="W11">
+        <v>0.06532137518684604</v>
+      </c>
+      <c r="X11">
+        <v>0.06419075768630611</v>
+      </c>
+      <c r="Y11">
+        <v>0.001130617500539929</v>
+      </c>
+      <c r="Z11">
+        <v>0.2202129211025229</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.06243392853800679</v>
+      </c>
+      <c r="AC11">
+        <v>-0.06243392853800679</v>
+      </c>
+      <c r="AD11">
+        <v>8.85</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>8.85</v>
+      </c>
+      <c r="AG11">
+        <v>-52.05</v>
+      </c>
+      <c r="AH11">
+        <v>0.09194805194805195</v>
+      </c>
+      <c r="AI11">
+        <v>0.0596964586846543</v>
+      </c>
+      <c r="AJ11">
+        <v>-1.472418670438472</v>
+      </c>
+      <c r="AK11">
+        <v>-0.5958786491127647</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
         <v>0</v>
       </c>
     </row>
